--- a/data/trans_bre/Hacinamiento_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Clase-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 4,06</t>
+          <t>-7,6; 4,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 9,91</t>
+          <t>-1,59; 9,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 13,67</t>
+          <t>0,17; 12,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 6,96</t>
+          <t>-2,07; 6,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,65; 174,18</t>
+          <t>-83,64; 189,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,08; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,01; 618,09</t>
+          <t>-55,26; 403,36</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 1,23</t>
+          <t>-11,62; 1,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 9,57</t>
+          <t>-6,37; 9,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 8,84</t>
+          <t>-3,55; 8,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 2,71</t>
+          <t>-8,24; 2,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,17; 53,13</t>
+          <t>-91,15; 85,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 326,5</t>
+          <t>-66,36; 294,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,99; 327,67</t>
+          <t>-52,53; 367,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-89,99; 137,87</t>
+          <t>-87,48; 146,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 6,49</t>
+          <t>-5,11; 6,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 12,0</t>
+          <t>-6,08; 11,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 15,26</t>
+          <t>-2,2; 14,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 15,3</t>
+          <t>0,7; 14,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,12; 318,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-45,88; 224,84</t>
+          <t>-47,72; 216,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,29; 990,62</t>
+          <t>-45,72; 897,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-78,51; —</t>
+          <t>-59,65; —</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,86</t>
+          <t>-4,31; 3,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 8,01</t>
+          <t>-3,82; 7,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 5,54</t>
+          <t>-3,88; 5,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,73; -0,49</t>
+          <t>-10,31; -0,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 150,28</t>
+          <t>-62,86; 134,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 120,1</t>
+          <t>-33,53; 114,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,35; 129,4</t>
+          <t>-42,63; 120,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,86; -0,81</t>
+          <t>-80,8; -6,93</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 6,58</t>
+          <t>-11,46; 6,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 3,11</t>
+          <t>-12,19; 3,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 4,61</t>
+          <t>-10,31; 5,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 6,61</t>
+          <t>-6,66; 6,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 57,48</t>
+          <t>-58,67; 63,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-67,29; 32,73</t>
+          <t>-65,99; 40,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,9; 50,73</t>
+          <t>-55,5; 61,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 88,59</t>
+          <t>-46,8; 82,26</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 8,12</t>
+          <t>-9,45; 7,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 10,86</t>
+          <t>-7,46; 11,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 10,02</t>
+          <t>-3,59; 9,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,29; -0,53</t>
+          <t>-19,82; -0,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 120,92</t>
+          <t>-59,49; 115,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,18; 154,02</t>
+          <t>-50,5; 174,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,75; 818,18</t>
+          <t>-65,7; 734,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,69; 4,34</t>
+          <t>-83,64; 6,22</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,97</t>
+          <t>-3,86; 1,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,17</t>
+          <t>-2,22; 4,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,45</t>
+          <t>-0,66; 4,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,43</t>
+          <t>-4,53; 0,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 14,09</t>
+          <t>-42,54; 19,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 55,68</t>
+          <t>-21,07; 53,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 79,58</t>
+          <t>-9,51; 82,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 8,4</t>
+          <t>-49,0; 4,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Clase-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 4,47</t>
+          <t>-6,98; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 9,23</t>
+          <t>-1,94; 9,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 12,82</t>
+          <t>0,68; 13,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,43</t>
+          <t>-2,2; 6,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-83,64; 189,93</t>
+          <t>-82,14; 192,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-57,01; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,26; 403,36</t>
+          <t>-51,73; 431,31</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 1,93</t>
+          <t>-11,16; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 9,42</t>
+          <t>-5,66; 8,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 8,0</t>
+          <t>-4,02; 8,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 2,87</t>
+          <t>-7,24; 2,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,15; 85,47</t>
+          <t>-89,36; 84,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,36; 294,01</t>
+          <t>-64,17; 320,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,53; 367,28</t>
+          <t>-58,71; 338,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,48; 146,57</t>
+          <t>-86,46; 127,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 6,51</t>
+          <t>-5,03; 6,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 11,67</t>
+          <t>-6,14; 11,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 14,31</t>
+          <t>-2,98; 14,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 14,66</t>
+          <t>1,03; 14,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,12; 318,02</t>
+          <t>-82,41; 404,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,72; 216,54</t>
+          <t>-50,93; 288,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 897,64</t>
+          <t>-59,37; 673,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,65; —</t>
+          <t>-34,83; —</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 3,71</t>
+          <t>-3,87; 4,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 7,54</t>
+          <t>-4,05; 8,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 5,42</t>
+          <t>-3,96; 5,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -0,97</t>
+          <t>-10,78; -0,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 134,64</t>
+          <t>-60,08; 166,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,53; 114,8</t>
+          <t>-32,54; 117,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 120,16</t>
+          <t>-43,68; 110,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,8; -6,93</t>
+          <t>-81,61; -5,91</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 6,81</t>
+          <t>-10,84; 6,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 3,96</t>
+          <t>-12,39; 3,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 5,21</t>
+          <t>-9,9; 4,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 6,36</t>
+          <t>-6,5; 6,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,67; 63,21</t>
+          <t>-57,23; 62,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 40,26</t>
+          <t>-66,74; 37,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 61,66</t>
+          <t>-56,38; 50,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,8; 82,26</t>
+          <t>-46,17; 93,91</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 7,55</t>
+          <t>-8,33; 7,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 11,91</t>
+          <t>-7,95; 11,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 9,28</t>
+          <t>-3,53; 9,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,82; -0,45</t>
+          <t>-18,22; -0,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 115,48</t>
+          <t>-56,15; 117,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 174,44</t>
+          <t>-52,09; 169,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 734,76</t>
+          <t>-63,99; 776,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,64; 6,22</t>
+          <t>-84,74; 4,75</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,36</t>
+          <t>-3,95; 1,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,06</t>
+          <t>-1,9; 4,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,67</t>
+          <t>-0,71; 4,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,33</t>
+          <t>-4,88; 0,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 19,53</t>
+          <t>-43,03; 18,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 53,71</t>
+          <t>-18,12; 56,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 82,37</t>
+          <t>-9,74; 85,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 4,95</t>
+          <t>-50,16; 5,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 4,39</t>
+          <t>-7,74; 4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 9,72</t>
+          <t>-1,16; 9,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 13,86</t>
+          <t>0,25; 13,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 6,62</t>
+          <t>-1,27; 7,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-82,14; 192,04</t>
+          <t>-84,65; 174,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,01; —</t>
+          <t>-51,08; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 431,31</t>
+          <t>-40,14; 675,29</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,31</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-40,95%</t>
+          <t>-34,42%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 1,85</t>
+          <t>-12,73; 1,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 8,95</t>
+          <t>-5,53; 9,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 8,07</t>
+          <t>-3,46; 8,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 2,7</t>
+          <t>-7,9; 3,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,36; 84,61</t>
+          <t>-91,17; 53,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 320,68</t>
+          <t>-62,91; 326,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,71; 338,05</t>
+          <t>-53,99; 327,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,46; 127,72</t>
+          <t>-89,31; 183,34</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,86</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>323,29%</t>
+          <t>303,12%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 6,65</t>
+          <t>-5,43; 6,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 11,83</t>
+          <t>-5,48; 12,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 14,28</t>
+          <t>-1,62; 15,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 14,97</t>
+          <t>0,52; 14,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,41; 404,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 288,2</t>
+          <t>-45,88; 224,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 673,2</t>
+          <t>-51,29; 990,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,83; —</t>
+          <t>-79,02; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,43</t>
+          <t>-4,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-58,55%</t>
+          <t>-51,3%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 4,15</t>
+          <t>-4,2; 3,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 8,36</t>
+          <t>-3,57; 8,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,38</t>
+          <t>-4,29; 5,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -0,74</t>
+          <t>-9,76; 0,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,08; 166,08</t>
+          <t>-62,83; 150,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 117,09</t>
+          <t>-30,04; 120,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 110,09</t>
+          <t>-46,35; 129,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,61; -5,91</t>
+          <t>-77,83; 6,77</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 6,87</t>
+          <t>-11,7; 6,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 3,38</t>
+          <t>-13,01; 3,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 4,81</t>
+          <t>-11,42; 4,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 6,93</t>
+          <t>-4,7; 7,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 62,62</t>
+          <t>-59,04; 57,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 37,53</t>
+          <t>-67,29; 32,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,38; 50,78</t>
+          <t>-58,9; 50,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 93,91</t>
+          <t>-35,68; 113,39</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-9,1</t>
+          <t>-8,35</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-58,02%</t>
+          <t>-54,98%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 7,94</t>
+          <t>-8,3; 8,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 11,77</t>
+          <t>-8,69; 10,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 9,53</t>
+          <t>-3,26; 10,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -0,2</t>
+          <t>-17,82; 0,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 117,3</t>
+          <t>-56,71; 120,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 169,97</t>
+          <t>-56,18; 154,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-63,99; 776,28</t>
+          <t>-68,75; 818,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,74; 4,75</t>
+          <t>-85,88; 7,72</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,1</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-26,01%</t>
+          <t>-17,72%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,13</t>
+          <t>-4,05; 0,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 4,23</t>
+          <t>-1,99; 4,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,59</t>
+          <t>-0,46; 4,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 0,23</t>
+          <t>-4,07; 1,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,03; 18,25</t>
+          <t>-43,92; 14,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 56,21</t>
+          <t>-18,67; 55,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 85,02</t>
+          <t>-6,85; 79,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-50,16; 5,05</t>
+          <t>-44,39; 20,04</t>
         </is>
       </c>
     </row>
